--- a/ontology/ccasp/RFCC_CCaSP_Model_v0.1.xlsx
+++ b/ontology/ccasp/RFCC_CCaSP_Model_v0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories_GitHub\ucm\ontology\ccasp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D42A4C2A-D17D-460B-9134-2ABE6250E93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACAC0D2-8F34-4BE9-96ED-B64A91FE7305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="1260" windowWidth="25935" windowHeight="13755" activeTab="1" xr2:uid="{755EA84D-CF44-4D7E-91CD-3D393DC665D3}"/>
+    <workbookView xWindow="450" yWindow="4035" windowWidth="28410" windowHeight="9585" firstSheet="1" activeTab="5" xr2:uid="{755EA84D-CF44-4D7E-91CD-3D393DC665D3}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Definition" sheetId="4" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="03_Shared Characteristics" sheetId="2" r:id="rId3"/>
     <sheet name="04_Shared_Capabilities" sheetId="1" r:id="rId4"/>
     <sheet name="05_Role_to_Capability" sheetId="5" r:id="rId5"/>
+    <sheet name="06_Terminology_Bindings" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="244">
   <si>
     <t>Care Coordination and Support Personnel (CCaSP) - Shared Capabilities</t>
   </si>
@@ -201,9 +202,6 @@
     <t>Care Coordinator</t>
   </si>
   <si>
-    <t>Individuals responsible for organizing, monitoring, and facilitating delivery of services across healthcare providers and settings to ensure continuity, efficiency, and achievement of patient-centered goals. Activities commonly include care planning, communication management, referrals, follow-up, and transitions of care.</t>
-  </si>
-  <si>
     <t>CMS</t>
   </si>
   <si>
@@ -243,13 +241,7 @@
     <t>Individuals responsible for assessing needs, coordinating services, facilitating access to health and social resources, monitoring progress, documenting outcomes, and supporting individuals in achieving care or service goals.  Case workers often operate across healthcare, behavioral health, social services, community programs, and public assistance systems and may perform case management functions depending on organizational scope.</t>
   </si>
   <si>
-    <t>Individuals responsible for helping individuals identity, access, coordinate, and engage with community-based, social, public, and supportive resources to address health-related social needs and improve wellbeing across care settings and organizations.</t>
-  </si>
-  <si>
     <t>Community Outreach Worker</t>
-  </si>
-  <si>
-    <t>Individuals responsible for engaging individuals and communities, conducting outreach, providing education and resource awareness, identity unmet needs, facilitating connections to healthcare, social, and community services, and supporting engagement with available programs and resources.</t>
   </si>
   <si>
     <t>Community Resource Navigator / Resource Navigator (RNAV)</t>
@@ -273,6 +265,9 @@
     <t>Value</t>
   </si>
   <si>
+    <t>RFCC</t>
+  </si>
+  <si>
     <t>RFCC ID</t>
   </si>
   <si>
@@ -300,15 +295,9 @@
     <t>Includes</t>
   </si>
   <si>
-    <t>Care Coordinator, Care Navigator, Case Manager, Case Worker, Patient Navigator, Community Resource Navigator, Community Outreach Worker, Community Health Worker</t>
-  </si>
-  <si>
     <t>Excludes</t>
   </si>
   <si>
-    <t>Tools, services, diagnosis, direct clinical treatment</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -339,13 +328,7 @@
     <t>Monitor</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Case Manager</t>
-  </si>
-  <si>
-    <t>Optional</t>
   </si>
   <si>
     <t>Referral Coordinator</t>
@@ -375,20 +358,517 @@
 AHRQ</t>
   </si>
   <si>
-    <t>Individuals responsible for identifying, organizing, and connecting individuals to available healthcare, social, community, financil, and supportive resources and providing information to support service access and management.</t>
-  </si>
-  <si>
     <t>Individuals with lived experience who provide support, mentorship, advocacy, education, and service navigation to help individuals engage in care, recovery, self-management, and achievement of personal goals.</t>
   </si>
   <si>
     <t>SAMHSA</t>
+  </si>
+  <si>
+    <t>Workbook Version</t>
+  </si>
+  <si>
+    <t>v0.1</t>
+  </si>
+  <si>
+    <t>Last Updated</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>UCM</t>
+  </si>
+  <si>
+    <t>Respository</t>
+  </si>
+  <si>
+    <t>ucm-repo</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Natacha Fernandez</t>
+  </si>
+  <si>
+    <t>Steward</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Initial CCaSP ontology model</t>
+  </si>
+  <si>
+    <t>Care Coordinator, Care Navigator, Case Manager, Case Worker, Patient Navigator, Community Resource Navigator, Community Outreach Worker, Community Health Worker, etc.</t>
+  </si>
+  <si>
+    <t>Tools, services, diagnosis, direct clinical treatment authority</t>
+  </si>
+  <si>
+    <t>Connect</t>
+  </si>
+  <si>
+    <t>Communicate</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>Follow Up</t>
+  </si>
+  <si>
+    <t>Advocate</t>
+  </si>
+  <si>
+    <t>Reduce Barriers</t>
+  </si>
+  <si>
+    <t>Definitions:</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Primary (P)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Core expected function of the role</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Secondary (S)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Common supporting function</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Situational (ST)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = Depends on setting, program, scope, or implementation</t>
+    </r>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>Capability Profile Notes</t>
+  </si>
+  <si>
+    <t>Strongest cross-domain coordination profile; emphasizes coordination across healthcare, behavioral health, social care, and community services.</t>
+  </si>
+  <si>
+    <t>Strong emphasis on navigation, advocacy, community connection, engagement, and barrier reduction.</t>
+  </si>
+  <si>
+    <t>Emphasizes advocacy, engagement, lived experience, and support over formal coordination activities.</t>
+  </si>
+  <si>
+    <t>Broad coordination profile emphasizing care planning, communication, referrals, follow-up, monitoring, and continuity across settings and organizations.</t>
+  </si>
+  <si>
+    <t>Navigation-first role emphasizing guidance, access, service linkage, barrier reduction, and progression through healthcare and related services.</t>
+  </si>
+  <si>
+    <t>Comprehensive management profile emphasizing assessment, planning, coordination, monitoring, evaluation, and longitudinal support of care goals.</t>
+  </si>
+  <si>
+    <t>Broad support and coordination profile emphasizing needs assessment, service facilitation, monitoring, and achievement of care service goals.</t>
+  </si>
+  <si>
+    <t>Navigation-first role emphasizing identification of recources, service connection, and facilitating access to community and supportive services.</t>
+  </si>
+  <si>
+    <t>Outreach and engagement profile emphasizing education, community connection, unmet need identificaiton, and linkage to services.</t>
+  </si>
+  <si>
+    <t>Emphasized referral management, documentation, communication, follow-up, and continuity more than assessment and formal care planning.</t>
+  </si>
+  <si>
+    <t>Individuals responsible for helping individuals identify, access, coordinate, and engage with community-based, social, public, and supportive resources to address health-related social needs and improve wellbeing across care settings and organizations.</t>
+  </si>
+  <si>
+    <t>Individuals responsible for engaging individuals and communities, conducting outreach, providing education and resource awareness, identify unmet needs, facilitating connections to healthcare, social, and community services, and supporting engagement with available programs and resources.</t>
+  </si>
+  <si>
+    <t>Patient-facing navigation profile emphasizing engagment, access, communication, adherence, and timely completion of services and treatment.</t>
+  </si>
+  <si>
+    <t>Individuals responsible for identifying, organizing, and connecting individuals to available healthcare, social, community, financial, and supportive resources and providing information to support service access and management.</t>
+  </si>
+  <si>
+    <t>Focused on identifying, organizing, and connecting resources rather than longitudinal coordination or formal care management.</t>
+  </si>
+  <si>
+    <t>Individuals responsible for organizing, monitoring, and facilitating delivery of services across healthcare providers and settings to ensure continuity, efficiency, and achievement of person-centered goals. Activities commonly include care planning, communication management, referrals, follow-up, and transitions of care.</t>
+  </si>
+  <si>
+    <t>Role ID</t>
+  </si>
+  <si>
+    <t>ROLE-001</t>
+  </si>
+  <si>
+    <t>ROLE-002</t>
+  </si>
+  <si>
+    <t>ROLE-003</t>
+  </si>
+  <si>
+    <t>ROLE-004</t>
+  </si>
+  <si>
+    <t>ROLE-005</t>
+  </si>
+  <si>
+    <t>ROLE-006</t>
+  </si>
+  <si>
+    <t>ROLE-007</t>
+  </si>
+  <si>
+    <t>ROLE-008</t>
+  </si>
+  <si>
+    <t>ROLE-009</t>
+  </si>
+  <si>
+    <t>ROLE-010</t>
+  </si>
+  <si>
+    <t>ROLE-011</t>
+  </si>
+  <si>
+    <t>ROLE-012</t>
+  </si>
+  <si>
+    <t>CHAR-001</t>
+  </si>
+  <si>
+    <t>CHAR-002</t>
+  </si>
+  <si>
+    <t>CHAR-003</t>
+  </si>
+  <si>
+    <t>CHAR-004</t>
+  </si>
+  <si>
+    <t>CHAR-005</t>
+  </si>
+  <si>
+    <t>CHAR-006</t>
+  </si>
+  <si>
+    <t>CHAR-007</t>
+  </si>
+  <si>
+    <t>CHAR-008</t>
+  </si>
+  <si>
+    <t>CHAR-009</t>
+  </si>
+  <si>
+    <t>CHAR-010</t>
+  </si>
+  <si>
+    <t>CHAR-011</t>
+  </si>
+  <si>
+    <t>Capability</t>
+  </si>
+  <si>
+    <t>CAP-001</t>
+  </si>
+  <si>
+    <t>CAP-002</t>
+  </si>
+  <si>
+    <t>CAP-003</t>
+  </si>
+  <si>
+    <t>CAP-004</t>
+  </si>
+  <si>
+    <t>CAP-005</t>
+  </si>
+  <si>
+    <t>CAP-006</t>
+  </si>
+  <si>
+    <t>CAP-007</t>
+  </si>
+  <si>
+    <t>CAP-008</t>
+  </si>
+  <si>
+    <t>SNOMED CT</t>
+  </si>
+  <si>
+    <t>LOINC</t>
+  </si>
+  <si>
+    <t>CAP ID</t>
+  </si>
+  <si>
+    <t>CHAR ID</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Purpose:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Maps RFCC/UCM concepts to external terminology and interoperability standards.</t>
+    </r>
+  </si>
+  <si>
+    <t>Concept Nane</t>
+  </si>
+  <si>
+    <t>Source Tab</t>
+  </si>
+  <si>
+    <t>FHIR Resource</t>
+  </si>
+  <si>
+    <t>Binding Status</t>
+  </si>
+  <si>
+    <t>01_Definition</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>PractitionerRole</t>
+  </si>
+  <si>
+    <t>Canonical umbrella actor concept</t>
+  </si>
+  <si>
+    <t>02_Roles</t>
+  </si>
+  <si>
+    <t>Coordination-focused actor</t>
+  </si>
+  <si>
+    <t>Navigation-focused actor</t>
+  </si>
+  <si>
+    <t>Longitudinal care management</t>
+  </si>
+  <si>
+    <t>Patient guidance and access</t>
+  </si>
+  <si>
+    <t>Community engagement and support</t>
+  </si>
+  <si>
+    <t>Cross-domain coordination</t>
+  </si>
+  <si>
+    <t>Service facilitation and monitoring</t>
+  </si>
+  <si>
+    <t>Resource navigation and access</t>
+  </si>
+  <si>
+    <t>Outreach and engagement</t>
+  </si>
+  <si>
+    <t>Referral workflow participation</t>
+  </si>
+  <si>
+    <t>Resource identification and connection</t>
+  </si>
+  <si>
+    <t>Lived experience support</t>
+  </si>
+  <si>
+    <t>Human Actor</t>
+  </si>
+  <si>
+    <t>03_Shared_Characteristics</t>
+  </si>
+  <si>
+    <t>Role performed by a person</t>
+  </si>
+  <si>
+    <t>CarePlan</t>
+  </si>
+  <si>
+    <t>Participation in plan creation, contribution, execution, or monitoring</t>
+  </si>
+  <si>
+    <t>ServiceRequest</t>
+  </si>
+  <si>
+    <t>Referral initiation, receipt, facilitation, tracking, or closure</t>
+  </si>
+  <si>
+    <t>Monitoring and Follow-Up</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Tracking engagement and outcomes</t>
+  </si>
+  <si>
+    <t>04_Shared_Capabilities</t>
+  </si>
+  <si>
+    <t>CareTeam</t>
+  </si>
+  <si>
+    <t>Organize services and activities</t>
+  </si>
+  <si>
+    <t>Support access to services</t>
+  </si>
+  <si>
+    <t>Identify needs and barriers</t>
+  </si>
+  <si>
+    <t>Referral-related activities</t>
+  </si>
+  <si>
+    <t>Work with care plans</t>
+  </si>
+  <si>
+    <t>Track progress and outcomes</t>
+  </si>
+  <si>
+    <t>Link individuals to services</t>
+  </si>
+  <si>
+    <t>Exchange information</t>
+  </si>
+  <si>
+    <t>CAP-009</t>
+  </si>
+  <si>
+    <t>DocumentReference</t>
+  </si>
+  <si>
+    <t>Record coordination activities</t>
+  </si>
+  <si>
+    <t>CAP-010</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Support continuity and completion</t>
+  </si>
+  <si>
+    <t>CAP-011</t>
+  </si>
+  <si>
+    <t>Support goals and participation</t>
+  </si>
+  <si>
+    <t>CAP-012</t>
+  </si>
+  <si>
+    <t>Address access and engagement obstacles</t>
+  </si>
+  <si>
+    <t>Binding Type</t>
+  </si>
+  <si>
+    <t>Verification Status</t>
+  </si>
+  <si>
+    <t>Source Authority</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Not Reviewed</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,8 +919,21 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,8 +964,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="23">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -502,36 +1001,6 @@
       <right style="hair">
         <color rgb="FF666666"/>
       </right>
-      <top style="thin">
-        <color rgb="FF666666"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF666666"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF666666"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF666666"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF666666"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF666666"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF666666"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF666666"/>
-      </right>
       <top style="hair">
         <color rgb="FF666666"/>
       </top>
@@ -601,17 +1070,6 @@
       <right style="thin">
         <color rgb="FF666666"/>
       </right>
-      <top style="thin">
-        <color rgb="FF666666"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF666666"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -622,26 +1080,6 @@
         <color rgb="FF666666"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF666666"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF666666"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF666666"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color rgb="FF666666"/>
       </bottom>
@@ -701,15 +1139,6 @@
       <bottom style="thin">
         <color rgb="FF666666"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF666666"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -756,26 +1185,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF666666"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -784,73 +1233,43 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -859,17 +1278,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -880,9 +1290,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -891,15 +1301,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1235,92 +1670,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E88CC5-A71C-4FF6-AFF2-41AB29914075}">
-  <dimension ref="A2:B11"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="38" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" style="25" customWidth="1"/>
     <col min="2" max="2" width="84" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="38"/>
+    <col min="3" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="37" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B3" s="36">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
+    </row>
+    <row r="11" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="39" t="s">
+      <c r="B12" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
+    <row r="13" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="B14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+    <row r="17" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
+      <c r="B18" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+    <row r="20" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1330,194 +1841,281 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5426B14-B35F-4A87-8D0A-8D2DCA6588F1}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.42578125" customWidth="1"/>
-    <col min="2" max="2" width="87" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="3" max="3" width="87" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="39.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="36"/>
-    </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="40"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="29"/>
+      <c r="B2" s="17"/>
       <c r="C2" s="17"/>
-    </row>
-    <row r="3" spans="1:3" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="17"/>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" ht="81.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="19"/>
-    </row>
-    <row r="4" spans="1:3" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="9"/>
+    </row>
+    <row r="4" spans="1:5" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="C4" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="21" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="E4" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="C5" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="32" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="E10" s="39" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="E13" s="39" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="32" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="47" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>110</v>
+      <c r="E16" s="39" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8484003/" xr:uid="{4FD69FC1-71CF-41DD-B7EF-29D92022BA69}"/>
-    <hyperlink ref="C8" r:id="rId2" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC4121958/" xr:uid="{31182C78-431C-4DA8-A450-7784863C1A35}"/>
-    <hyperlink ref="C9" r:id="rId3" display="https://hdsbpc.cdc.gov/s/article/Community-Health-Workers-New" xr:uid="{858F8AF8-00B4-4785-8A97-E43EEC82BD5E}"/>
-    <hyperlink ref="C10" r:id="rId4" display="https://www.cms.gov/priorities/innovation/key-concepts/care-coordination" xr:uid="{04012564-8844-45BD-9B6C-B2AF920543F0}"/>
-    <hyperlink ref="C11" r:id="rId5" display="https://cmsa.org/who-we-are/what-is-a-case-manager/" xr:uid="{DE750D75-F77D-4DC5-8E79-518D9FC51E90}"/>
-    <hyperlink ref="C12" r:id="rId6" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9125772/" xr:uid="{5FA32D13-3C42-4F7B-9A00-895D508F1525}"/>
-    <hyperlink ref="C13" r:id="rId7" display="https://www.ncbi.nlm.nih.gov/sites/books/NBK555582/" xr:uid="{EC7242FF-6F87-4C00-A4FF-1867AC4962F2}"/>
-    <hyperlink ref="C5" r:id="rId8" display="https://www.cms.gov/priorities/innovation/key-concepts/care-coordination" xr:uid="{E9188CA2-B7A3-456F-B8F1-67B1FCA92F12}"/>
-    <hyperlink ref="C16" r:id="rId9" xr:uid="{556DA811-B49F-4972-9B0D-728F16C46FED}"/>
+    <hyperlink ref="D6" r:id="rId1" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC8484003/" xr:uid="{4FD69FC1-71CF-41DD-B7EF-29D92022BA69}"/>
+    <hyperlink ref="D8" r:id="rId2" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC4121958/" xr:uid="{31182C78-431C-4DA8-A450-7784863C1A35}"/>
+    <hyperlink ref="D9" r:id="rId3" display="https://hdsbpc.cdc.gov/s/article/Community-Health-Workers-New" xr:uid="{858F8AF8-00B4-4785-8A97-E43EEC82BD5E}"/>
+    <hyperlink ref="D10" r:id="rId4" display="https://www.cms.gov/priorities/innovation/key-concepts/care-coordination" xr:uid="{04012564-8844-45BD-9B6C-B2AF920543F0}"/>
+    <hyperlink ref="D11" r:id="rId5" display="https://cmsa.org/who-we-are/what-is-a-case-manager/" xr:uid="{DE750D75-F77D-4DC5-8E79-518D9FC51E90}"/>
+    <hyperlink ref="D12" r:id="rId6" display="https://pmc.ncbi.nlm.nih.gov/articles/PMC9125772/" xr:uid="{5FA32D13-3C42-4F7B-9A00-895D508F1525}"/>
+    <hyperlink ref="D13" r:id="rId7" display="https://www.ncbi.nlm.nih.gov/sites/books/NBK555582/" xr:uid="{EC7242FF-6F87-4C00-A4FF-1867AC4962F2}"/>
+    <hyperlink ref="D5" r:id="rId8" display="https://www.cms.gov/priorities/innovation/key-concepts/care-coordination" xr:uid="{E9188CA2-B7A3-456F-B8F1-67B1FCA92F12}"/>
+    <hyperlink ref="D16" r:id="rId9" xr:uid="{556DA811-B49F-4972-9B0D-728F16C46FED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1525,368 +2123,2085 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750CDF31-F20D-4924-8851-13B815C475D2}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
-    <col min="2" max="2" width="73.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.42578125" customWidth="1"/>
+    <col min="3" max="3" width="73.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:3" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="15"/>
-    </row>
-    <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="17"/>
-    </row>
-    <row r="3" spans="1:2" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="19"/>
-    </row>
-    <row r="4" spans="1:2" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B3" s="18"/>
+      <c r="C3" s="9"/>
+    </row>
+    <row r="4" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="C4" s="13" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+    <row r="5" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="C5" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="C14" s="5" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+    <row r="15" spans="1:3" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="C15" s="7" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B99C454E-80D9-4C60-BDC3-3E17AECCDA64}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.140625" customWidth="1"/>
-    <col min="2" max="2" width="72.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="72.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="19"/>
+      <c r="C1" s="20"/>
+    </row>
+    <row r="2" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-    </row>
-    <row r="3" spans="1:2" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="8"/>
+    </row>
+    <row r="3" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="7"/>
-    </row>
-    <row r="4" spans="1:2" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+    </row>
+    <row r="4" spans="1:3" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="C6" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="C7" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="C10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    <row r="12" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="C12" s="7" t="s">
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CEB275C-F496-4BFA-8287-5E712C977AA3}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="13.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="7" width="13.28515625" style="43"/>
+    <col min="1" max="1" width="31.5703125" customWidth="1"/>
+    <col min="2" max="7" width="14.42578125" style="30" customWidth="1"/>
+    <col min="8" max="13" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="41" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="25" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+    </row>
+    <row r="6" spans="1:13" s="28" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B6" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="G6" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="H6" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="L6" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="29" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="B8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L13" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L14" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" s="25" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="B16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="K16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L16" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M16" s="31" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="42" t="s">
+      <c r="B17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="B18" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="H18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="I18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="K18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="L18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="M18" s="31" t="s">
+        <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7636E63-7888-4D2F-8F45-49B6D5C5F641}">
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultColWidth="11.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
+    <col min="13" max="13" width="62.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="J2" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="K2" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="L2" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="M2" s="43" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F3" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="38" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="F5" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>97</v>
+      <c r="C4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
